--- a/Buch Bayrische Nächte/Zeitlinie.xlsx
+++ b/Buch Bayrische Nächte/Zeitlinie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julian Dauner\Documents\GitHub\pnpWiki\docs\Buch Bayrische Nächte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ECF81F3-7517-407B-89F7-AA9782377AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074B868B-F1AC-409B-99A3-EFAF7C2913BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="71">
   <si>
     <t>Year</t>
   </si>
@@ -98,9 +98,6 @@
     <t>Marina meets the Count Großberg to discuss the railcar project</t>
   </si>
   <si>
-    <t>Marina, Wilheml Freiherr, Aris</t>
-  </si>
-  <si>
     <t>October</t>
   </si>
   <si>
@@ -215,6 +212,37 @@
   <si>
     <t>Friedrich has passed the police exams in Munich and is relaxing with his Girlfriend Maria. 
 They talk about expectations of having a child.</t>
+  </si>
+  <si>
+    <t>Chapter 11</t>
+  </si>
+  <si>
+    <t>Chapter 12</t>
+  </si>
+  <si>
+    <t>Marina arrives home with ehr huibsand Wilhelm, there she meets her son and attendance. She later has sex with her 
+husband to cope, bad dreams keeping her awake.</t>
+  </si>
+  <si>
+    <t>Friedrich has been brought home and Marina rides home with Alexander, questioning Michael about the Wardens</t>
+  </si>
+  <si>
+    <t>Marina, Alexander, Michael, Wilhelm</t>
+  </si>
+  <si>
+    <t>Marina, Wilheml Freiherr, Philipp</t>
+  </si>
+  <si>
+    <t>Marina, Wilhelm, Philipp, Christoff, Gundel</t>
+  </si>
+  <si>
+    <t>Continuing Marina wakes up and remmebers the Coutns boat, searching in it for clues</t>
+  </si>
+  <si>
+    <t>Marina, Gundel</t>
+  </si>
+  <si>
+    <t>Josef, August, Ingenheim, Ashen-One, Lady of the Cult</t>
   </si>
 </sst>
 </file>
@@ -448,16 +476,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F56"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F58"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" customWidth="1"/>
-    <col min="5" max="5" width="105.85546875" customWidth="1"/>
-    <col min="6" max="6" width="70.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" customWidth="1"/>
+    <col min="5" max="5" width="105.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="70.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -470,132 +498,132 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1850</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C6">
         <v>4</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1842</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C9">
         <v>12</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1847</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C12">
         <v>1</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1855</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C15">
         <v>12</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1855</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C18">
         <v>7</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1857</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C21">
         <v>5</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1858</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C24">
         <v>19</v>
       </c>
@@ -603,19 +631,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1859</v>
       </c>
-      <c r="E25" s="1"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="1"/>
-    </row>
-    <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C27">
         <v>2</v>
       </c>
@@ -623,250 +649,287 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1862</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C30">
         <v>25</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F30" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1871</v>
       </c>
-      <c r="E31" s="1"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C33">
         <v>3</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1882</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C36">
         <v>10</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
-      </c>
-      <c r="E36" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F36" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C38">
         <v>28</v>
       </c>
       <c r="D38" t="s">
         <v>21</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" t="s">
         <v>26</v>
       </c>
-      <c r="F38" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C39">
         <v>29</v>
       </c>
       <c r="D39" t="s">
         <v>21</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39" t="s">
         <v>28</v>
       </c>
-      <c r="F39" t="s">
+    </row>
+    <row r="40" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C41">
         <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F41" t="s">
         <v>32</v>
       </c>
-      <c r="F41" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C42">
         <v>9</v>
       </c>
       <c r="D42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F42" t="s">
         <v>34</v>
       </c>
-      <c r="F42" t="s">
+    </row>
+    <row r="43" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D43" t="s">
+        <v>30</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F43" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D44" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D43" t="s">
-        <v>31</v>
-      </c>
-      <c r="E43" t="s">
-        <v>37</v>
-      </c>
-      <c r="F43" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="D44" t="s">
-        <v>36</v>
-      </c>
       <c r="E44" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F44" t="s">
         <v>40</v>
       </c>
-      <c r="F44" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C45">
         <v>10</v>
       </c>
       <c r="D45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F45" t="s">
         <v>43</v>
       </c>
-      <c r="F45" t="s">
+    </row>
+    <row r="46" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D46" t="s">
+        <v>41</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D47" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="D46" t="s">
-        <v>42</v>
-      </c>
-      <c r="E46" s="1" t="s">
+      <c r="E47" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F47" t="s">
         <v>46</v>
       </c>
-      <c r="F46" t="s">
+    </row>
+    <row r="48" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D48" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="D47" t="s">
-        <v>45</v>
-      </c>
-      <c r="E47" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F47" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="D48" t="s">
-        <v>48</v>
-      </c>
-      <c r="E48" s="1" t="s">
+    </row>
+    <row r="49" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D49" t="s">
-        <v>59</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F49" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C50">
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>58</v>
-      </c>
-      <c r="E50" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F50" t="s">
         <v>53</v>
       </c>
-      <c r="F50" t="s">
+    </row>
+    <row r="51" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D51" t="s">
+        <v>61</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F51" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="52" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C53">
+        <v>12</v>
+      </c>
+      <c r="D53" t="s">
+        <v>62</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F53" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="56" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C56">
+        <v>21</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="54" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C54">
-        <v>21</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="F56" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C57">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C58">
+        <v>25</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F54" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C55">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="56" spans="3:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="C56">
-        <v>25</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>56</v>
+      <c r="F58" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Buch Bayrische Nächte/Zeitlinie.xlsx
+++ b/Buch Bayrische Nächte/Zeitlinie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julian Dauner\Documents\GitHub\pnpWiki\docs\Buch Bayrische Nächte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074B868B-F1AC-409B-99A3-EFAF7C2913BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B437D2A-10C0-4FB1-AC11-5404F361E360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="90">
   <si>
     <t>Year</t>
   </si>
@@ -201,9 +201,6 @@
     <t>Aelxander goes to Munich to start studying at TUM at 16 years of age</t>
   </si>
   <si>
-    <t>Prologe</t>
-  </si>
-  <si>
     <t>Chaper 10</t>
   </si>
   <si>
@@ -233,16 +230,76 @@
     <t>Marina, Wilheml Freiherr, Philipp</t>
   </si>
   <si>
-    <t>Marina, Wilhelm, Philipp, Christoff, Gundel</t>
-  </si>
-  <si>
-    <t>Continuing Marina wakes up and remmebers the Coutns boat, searching in it for clues</t>
-  </si>
-  <si>
     <t>Marina, Gundel</t>
   </si>
   <si>
     <t>Josef, August, Ingenheim, Ashen-One, Lady of the Cult</t>
+  </si>
+  <si>
+    <t>Continuing Marina wakes up and remmebers the Counts boat, searching in it for clues</t>
+  </si>
+  <si>
+    <t>Friedrich, Marina, Alexander, Anna, Sabine, Helene Berthold, Nai, Sir Charles, etc.</t>
+  </si>
+  <si>
+    <t>Chapter 17</t>
+  </si>
+  <si>
+    <t>Chapter 14</t>
+  </si>
+  <si>
+    <t>Friedrich is talking with his demented mom about life</t>
+  </si>
+  <si>
+    <t>Friedrich, Walburga Pfeiffer</t>
+  </si>
+  <si>
+    <t>Marina, Wilhelm, Philipp, Christoff Bauer, Gundel Götz</t>
+  </si>
+  <si>
+    <t>Chapter 15</t>
+  </si>
+  <si>
+    <t>Chapter 13</t>
+  </si>
+  <si>
+    <t>Chapter 16</t>
+  </si>
+  <si>
+    <t>Chapter 18</t>
+  </si>
+  <si>
+    <t>Chapter 19</t>
+  </si>
+  <si>
+    <t>Chapter 21</t>
+  </si>
+  <si>
+    <t>Chapter 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting of the Wardens and </t>
+  </si>
+  <si>
+    <t>Murder on the Christmasmarket and ensuing chaos</t>
+  </si>
+  <si>
+    <t>Anna catches the killer while Alexander has visions through Maximilian</t>
+  </si>
+  <si>
+    <t>The Trio gets ist name and talks about their plans to make a decision</t>
+  </si>
+  <si>
+    <t>Anna gets trained by Sabine and learns about the Wardens</t>
+  </si>
+  <si>
+    <t>Josef and August learn more about the strange happenings around the Count von Tölz and run into Count von Ingenheim</t>
+  </si>
+  <si>
+    <t>Alexander wakes up from his visions</t>
+  </si>
+  <si>
+    <t>Alexander, Helene</t>
   </si>
 </sst>
 </file>
@@ -476,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.88671875" customWidth="1"/>
@@ -663,8 +720,11 @@
       <c r="C30">
         <v>25</v>
       </c>
+      <c r="D30" t="s">
+        <v>76</v>
+      </c>
       <c r="E30" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F30" t="s">
         <v>20</v>
@@ -709,7 +769,7 @@
         <v>22</v>
       </c>
       <c r="F36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -846,10 +906,10 @@
     </row>
     <row r="49" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
+        <v>57</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="F49" t="s">
         <v>50</v>
@@ -860,7 +920,7 @@
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>52</v>
@@ -871,24 +931,24 @@
     </row>
     <row r="51" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E51" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F51" t="s">
         <v>64</v>
-      </c>
-      <c r="F51" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="52" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
+        <v>61</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="F52" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -896,19 +956,47 @@
         <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F53" t="s">
-        <v>69</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C54">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>78</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C55">
+        <v>16</v>
+      </c>
+      <c r="D55" t="s">
+        <v>71</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F55" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="56" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C56">
         <v>21</v>
       </c>
+      <c r="D56" t="s">
+        <v>75</v>
+      </c>
       <c r="E56" s="1" t="s">
         <v>54</v>
       </c>
@@ -918,18 +1006,79 @@
     </row>
     <row r="57" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C57">
+        <v>22</v>
+      </c>
+      <c r="D57" t="s">
+        <v>77</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="58" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C58">
+        <v>23</v>
+      </c>
+      <c r="D58" t="s">
+        <v>70</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="59" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C59">
         <v>24</v>
       </c>
-    </row>
-    <row r="58" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C58">
+      <c r="D59" t="s">
+        <v>79</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F59" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="60" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D60" t="s">
+        <v>81</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D61" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C62">
         <v>25</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="D62" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F58" t="s">
-        <v>70</v>
+      <c r="F62" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="63" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C63">
+        <v>27</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F63" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Buch Bayrische Nächte/Zeitlinie.xlsx
+++ b/Buch Bayrische Nächte/Zeitlinie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julian Dauner\Documents\GitHub\pnpWiki\docs\Buch Bayrische Nächte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B437D2A-10C0-4FB1-AC11-5404F361E360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301687EC-E6EF-41B7-BDEB-896471AB2670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="95">
   <si>
     <t>Year</t>
   </si>
@@ -82,28 +82,18 @@
 and only hers, capsized. Sir Charles was bheind that but no one knew. The Regatta was cancled in the following years.</t>
   </si>
   <si>
-    <t>Alexander and his brother Ludwig play on a hill. Ludwig dares himself to drive down the hill with top speed.
-Alexander cheers him up. Ludwig dies, falling of and hitting his head on a rock.</t>
-  </si>
-  <si>
     <t>June</t>
   </si>
   <si>
     <t>Friedrich, Maria sr.</t>
   </si>
   <si>
-    <t>Chapter 2</t>
-  </si>
-  <si>
     <t>Marina meets the Count Großberg to discuss the railcar project</t>
   </si>
   <si>
     <t>October</t>
   </si>
   <si>
-    <t>Chapter 3</t>
-  </si>
-  <si>
     <t>Alexander finalizes the plans for the railcar project</t>
   </si>
   <si>
@@ -119,9 +109,6 @@
     <t>December</t>
   </si>
   <si>
-    <t>Chapter 4</t>
-  </si>
-  <si>
     <t>Friedrich has an episode, that almost kills him</t>
   </si>
   <si>
@@ -134,16 +121,10 @@
     <t>Friedrich, Trautl, Elke, Maria jr.</t>
   </si>
   <si>
-    <t>Chapter 5</t>
-  </si>
-  <si>
     <t>The trio meets for the first time and ascents the mountain with the Count Großberg</t>
   </si>
   <si>
     <t>Friedrich, Marina, Alexander, Count Großberg</t>
-  </si>
-  <si>
-    <t>Chapter 6</t>
   </si>
   <si>
     <t>Marina studies the books of Großberg while the other ski. She finds out more about werewolves with Alexander. 
@@ -153,27 +134,18 @@
     <t>Friedrich, Marina, Alexander, Count Großberg, Eric</t>
   </si>
   <si>
-    <t>Chapter 7</t>
-  </si>
-  <si>
     <t>Breakfast and ski donw the slope. Friedrich hurts himself because of the other Count. A heavy storm begins. Count Großberg leaves them in the Storm and darts off.</t>
   </si>
   <si>
     <t>Friedrich, Marina, Alexander, Count Großberg, Eric, Count Ingenheim</t>
   </si>
   <si>
-    <t>Chapter 8</t>
-  </si>
-  <si>
     <t>Friedrich scouts the chalet grounds and finds the Werewolf. He hurts it badly but gets sliced himself. The others save him.</t>
   </si>
   <si>
     <t>Friedrich, Marina, Alexander, Werewolf, Eric</t>
   </si>
   <si>
-    <t>Chapter 9</t>
-  </si>
-  <si>
     <t>Marina and Alexander prepare for another Werewolf attack and have to fight against Eric. They beat him down and make themselves ready.</t>
   </si>
   <si>
@@ -183,9 +155,6 @@
     <t>Anna Siebert, Sabine, Karl</t>
   </si>
   <si>
-    <t>Chapter 1</t>
-  </si>
-  <si>
     <t>Josef Fuchsberger suspects foul play after the suspects releases</t>
   </si>
   <si>
@@ -196,12 +165,6 @@
   </si>
   <si>
     <t>Count von Ingenheim, Fuchsberger und August try to uncover the lies of the Trio but are caught in the Web of the Cult in the Karmeliterkirche next to the Christmas Market</t>
-  </si>
-  <si>
-    <t>Aelxander goes to Munich to start studying at TUM at 16 years of age</t>
-  </si>
-  <si>
-    <t>Chaper 10</t>
   </si>
   <si>
     <t>Sabine and Karl, Dianists of the Wardens, catch Anna Siebert in the villa of the Count Grossberg in Tölz</t>
@@ -211,12 +174,6 @@
 They talk about expectations of having a child.</t>
   </si>
   <si>
-    <t>Chapter 11</t>
-  </si>
-  <si>
-    <t>Chapter 12</t>
-  </si>
-  <si>
     <t>Marina arrives home with ehr huibsand Wilhelm, there she meets her son and attendance. She later has sex with her 
 husband to cope, bad dreams keeping her awake.</t>
   </si>
@@ -242,12 +199,6 @@
     <t>Friedrich, Marina, Alexander, Anna, Sabine, Helene Berthold, Nai, Sir Charles, etc.</t>
   </si>
   <si>
-    <t>Chapter 17</t>
-  </si>
-  <si>
-    <t>Chapter 14</t>
-  </si>
-  <si>
     <t>Friedrich is talking with his demented mom about life</t>
   </si>
   <si>
@@ -257,27 +208,6 @@
     <t>Marina, Wilhelm, Philipp, Christoff Bauer, Gundel Götz</t>
   </si>
   <si>
-    <t>Chapter 15</t>
-  </si>
-  <si>
-    <t>Chapter 13</t>
-  </si>
-  <si>
-    <t>Chapter 16</t>
-  </si>
-  <si>
-    <t>Chapter 18</t>
-  </si>
-  <si>
-    <t>Chapter 19</t>
-  </si>
-  <si>
-    <t>Chapter 21</t>
-  </si>
-  <si>
-    <t>Chapter 20</t>
-  </si>
-  <si>
     <t xml:space="preserve">Meeting of the Wardens and </t>
   </si>
   <si>
@@ -300,6 +230,90 @@
   </si>
   <si>
     <t>Alexander, Helene</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>Book1/13</t>
+  </si>
+  <si>
+    <t>Book1/1</t>
+  </si>
+  <si>
+    <t>Book1/2</t>
+  </si>
+  <si>
+    <t>Book1/3</t>
+  </si>
+  <si>
+    <t>Book1/4</t>
+  </si>
+  <si>
+    <t>Book1/5</t>
+  </si>
+  <si>
+    <t>Book1/6</t>
+  </si>
+  <si>
+    <t>Book1/7</t>
+  </si>
+  <si>
+    <t>Book1/8</t>
+  </si>
+  <si>
+    <t>Book1/9</t>
+  </si>
+  <si>
+    <t>Book1/10</t>
+  </si>
+  <si>
+    <t>Book1/17</t>
+  </si>
+  <si>
+    <t>Book1/11</t>
+  </si>
+  <si>
+    <t>Book1/12</t>
+  </si>
+  <si>
+    <t>Book1/18</t>
+  </si>
+  <si>
+    <t>Book1/14</t>
+  </si>
+  <si>
+    <t>Book1/15</t>
+  </si>
+  <si>
+    <t>Book1/16</t>
+  </si>
+  <si>
+    <t>Book1/19</t>
+  </si>
+  <si>
+    <t>Book1/20</t>
+  </si>
+  <si>
+    <t>Book1/21</t>
+  </si>
+  <si>
+    <t>Book1/</t>
+  </si>
+  <si>
+    <t>Alexander trying a 'science' experiment. Older schoolboys bully him for it and his brother Ludwig intervenes, sends Alexander away. He hides and hears his brother die on accident after a push, blacks it from his memories.</t>
+  </si>
+  <si>
+    <t>Alexander goes to Munich to start studying at TUM at 16 years of age</t>
+  </si>
+  <si>
+    <t>Friedrich and Maria talk again about their life together, he notices her frustration forthe first time.</t>
+  </si>
+  <si>
+    <t>Maria sr. Dies, killing herself with Friedrichs weaopn, as he walks away. He hears the shot from outside of their appartment</t>
+  </si>
+  <si>
+    <t>Alois Großbërge von Tolnzar becomes the Werewolf Fury</t>
   </si>
 </sst>
 </file>
@@ -533,12 +547,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.88671875" customWidth="1"/>
     <col min="4" max="4" width="10.44140625" customWidth="1"/>
-    <col min="5" max="5" width="105.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="109.5546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="70.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -562,6 +576,14 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1632</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1850</v>
@@ -703,7 +725,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -713,7 +735,7 @@
     </row>
     <row r="29" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -721,364 +743,401 @@
         <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>1871</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>1882</v>
+      <c r="B34" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B35" t="s">
-        <v>14</v>
+      <c r="C35">
+        <v>6</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F35" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C36">
-        <v>10</v>
-      </c>
-      <c r="D36" t="s">
-        <v>51</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" t="s">
-        <v>65</v>
+      <c r="A36">
+        <v>1871</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C38">
-        <v>28</v>
-      </c>
-      <c r="D38" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C39">
-        <v>29</v>
-      </c>
-      <c r="D39" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F39" t="s">
-        <v>28</v>
+      <c r="A39">
+        <v>1882</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C41">
+        <v>10</v>
+      </c>
+      <c r="D41" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F41" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C43">
+        <v>28</v>
+      </c>
+      <c r="D43" t="s">
+        <v>70</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C44">
+        <v>29</v>
+      </c>
+      <c r="D44" t="s">
+        <v>70</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C46">
         <v>8</v>
       </c>
-      <c r="D41" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="1" t="s">
+      <c r="D46" t="s">
+        <v>71</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F46" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C47">
+        <v>9</v>
+      </c>
+      <c r="D47" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F47" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D48" t="s">
+        <v>72</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F48" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C42">
-        <v>9</v>
-      </c>
-      <c r="D42" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="1" t="s">
+    <row r="49" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D49" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F49" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="D43" t="s">
-        <v>30</v>
-      </c>
-      <c r="E43" s="1" t="s">
+    <row r="50" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C50">
+        <v>10</v>
+      </c>
+      <c r="D50" t="s">
+        <v>74</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F50" t="s">
         <v>36</v>
       </c>
-      <c r="F43" t="s">
+    </row>
+    <row r="51" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D51" t="s">
+        <v>75</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="D44" t="s">
-        <v>35</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F44" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C45">
-        <v>10</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="F51" t="s">
         <v>38</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F45" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="D46" t="s">
-        <v>41</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F46" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="D47" t="s">
-        <v>44</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F47" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="D48" t="s">
-        <v>47</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="D49" t="s">
-        <v>57</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F49" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="50" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C50">
-        <v>11</v>
-      </c>
-      <c r="D50" t="s">
-        <v>70</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F50" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D51" t="s">
-        <v>60</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F51" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="52" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="F52" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="53" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C53">
-        <v>12</v>
-      </c>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F53" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="54" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C54">
-        <v>13</v>
-      </c>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
         <v>78</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F54" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C55">
+        <v>11</v>
+      </c>
+      <c r="D55" t="s">
+        <v>79</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F55" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D56" t="s">
+        <v>80</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F56" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D57" t="s">
+        <v>81</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F57" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C58">
+        <v>12</v>
+      </c>
+      <c r="D58" t="s">
+        <v>81</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F58" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="59" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C59">
+        <v>13</v>
+      </c>
+      <c r="D59" t="s">
+        <v>82</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C60">
+        <v>16</v>
+      </c>
+      <c r="D60" t="s">
+        <v>83</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F60" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="61" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C61">
+        <v>21</v>
+      </c>
+      <c r="D61" t="s">
+        <v>84</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F61" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C62">
+        <v>22</v>
+      </c>
+      <c r="D62" t="s">
+        <v>85</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C63">
+        <v>23</v>
+      </c>
+      <c r="D63" t="s">
+        <v>79</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C64">
+        <v>24</v>
+      </c>
+      <c r="D64" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="55" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C55">
-        <v>16</v>
-      </c>
-      <c r="D55" t="s">
-        <v>71</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F55" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="56" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C56">
-        <v>21</v>
-      </c>
-      <c r="D56" t="s">
-        <v>75</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F56" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="57" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C57">
-        <v>22</v>
-      </c>
-      <c r="D57" t="s">
-        <v>77</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="58" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C58">
-        <v>23</v>
-      </c>
-      <c r="D58" t="s">
-        <v>70</v>
-      </c>
-      <c r="E58" s="1" t="s">
+      <c r="E64" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F64" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D65" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="59" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C59">
-        <v>24</v>
-      </c>
-      <c r="D59" t="s">
-        <v>79</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F59" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="60" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="D60" t="s">
-        <v>81</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="61" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="D61" t="s">
-        <v>80</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="62" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C62">
+      <c r="E65" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D66" t="s">
+        <v>88</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C67">
         <v>25</v>
       </c>
-      <c r="D62" t="s">
-        <v>3</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F62" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="63" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C63">
+      <c r="D67" t="s">
+        <v>89</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F67" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="68" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C68">
         <v>27</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F63" t="s">
+      <c r="D68" t="s">
         <v>89</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F68" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Buch Bayrische Nächte/Zeitlinie.xlsx
+++ b/Buch Bayrische Nächte/Zeitlinie.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julian Dauner\Documents\GitHub\pnpWiki\docs\Buch Bayrische Nächte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301687EC-E6EF-41B7-BDEB-896471AB2670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEDF0791-F904-4ED4-9EB5-669DAC9107BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="5205" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="97">
   <si>
     <t>Year</t>
   </si>
@@ -134,9 +134,6 @@
     <t>Friedrich, Marina, Alexander, Count Großberg, Eric</t>
   </si>
   <si>
-    <t>Breakfast and ski donw the slope. Friedrich hurts himself because of the other Count. A heavy storm begins. Count Großberg leaves them in the Storm and darts off.</t>
-  </si>
-  <si>
     <t>Friedrich, Marina, Alexander, Count Großberg, Eric, Count Ingenheim</t>
   </si>
   <si>
@@ -174,146 +171,155 @@
 They talk about expectations of having a child.</t>
   </si>
   <si>
-    <t>Marina arrives home with ehr huibsand Wilhelm, there she meets her son and attendance. She later has sex with her 
+    <t>Friedrich has been brought home and Marina rides home with Alexander, questioning Michael about the Wardens</t>
+  </si>
+  <si>
+    <t>Marina, Alexander, Michael, Wilhelm</t>
+  </si>
+  <si>
+    <t>Marina, Wilheml Freiherr, Philipp</t>
+  </si>
+  <si>
+    <t>Marina, Gundel</t>
+  </si>
+  <si>
+    <t>Josef, August, Ingenheim, Ashen-One, Lady of the Cult</t>
+  </si>
+  <si>
+    <t>Continuing Marina wakes up and remmebers the Counts boat, searching in it for clues</t>
+  </si>
+  <si>
+    <t>Friedrich, Marina, Alexander, Anna, Sabine, Helene Berthold, Nai, Sir Charles, etc.</t>
+  </si>
+  <si>
+    <t>Friedrich is talking with his demented mom about life</t>
+  </si>
+  <si>
+    <t>Friedrich, Walburga Pfeiffer</t>
+  </si>
+  <si>
+    <t>Marina, Wilhelm, Philipp, Christoff Bauer, Gundel Götz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting of the Wardens and </t>
+  </si>
+  <si>
+    <t>Murder on the Christmasmarket and ensuing chaos</t>
+  </si>
+  <si>
+    <t>Anna catches the killer while Alexander has visions through Maximilian</t>
+  </si>
+  <si>
+    <t>The Trio gets ist name and talks about their plans to make a decision</t>
+  </si>
+  <si>
+    <t>Anna gets trained by Sabine and learns about the Wardens</t>
+  </si>
+  <si>
+    <t>Josef and August learn more about the strange happenings around the Count von Tölz and run into Count von Ingenheim</t>
+  </si>
+  <si>
+    <t>Alexander wakes up from his visions</t>
+  </si>
+  <si>
+    <t>Alexander, Helene</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>Book1/13</t>
+  </si>
+  <si>
+    <t>Book1/1</t>
+  </si>
+  <si>
+    <t>Book1/2</t>
+  </si>
+  <si>
+    <t>Book1/3</t>
+  </si>
+  <si>
+    <t>Book1/4</t>
+  </si>
+  <si>
+    <t>Book1/5</t>
+  </si>
+  <si>
+    <t>Book1/6</t>
+  </si>
+  <si>
+    <t>Book1/7</t>
+  </si>
+  <si>
+    <t>Book1/8</t>
+  </si>
+  <si>
+    <t>Book1/9</t>
+  </si>
+  <si>
+    <t>Book1/10</t>
+  </si>
+  <si>
+    <t>Book1/17</t>
+  </si>
+  <si>
+    <t>Book1/11</t>
+  </si>
+  <si>
+    <t>Book1/12</t>
+  </si>
+  <si>
+    <t>Book1/18</t>
+  </si>
+  <si>
+    <t>Book1/14</t>
+  </si>
+  <si>
+    <t>Book1/15</t>
+  </si>
+  <si>
+    <t>Book1/16</t>
+  </si>
+  <si>
+    <t>Book1/19</t>
+  </si>
+  <si>
+    <t>Book1/20</t>
+  </si>
+  <si>
+    <t>Book1/21</t>
+  </si>
+  <si>
+    <t>Book1/</t>
+  </si>
+  <si>
+    <t>Alexander trying a 'science' experiment. Older schoolboys bully him for it and his brother Ludwig intervenes, sends Alexander away. He hides and hears his brother die on accident after a push, blacks it from his memories.</t>
+  </si>
+  <si>
+    <t>Alexander goes to Munich to start studying at TUM at 16 years of age</t>
+  </si>
+  <si>
+    <t>Friedrich and Maria talk again about their life together, he notices her frustration forthe first time.</t>
+  </si>
+  <si>
+    <t>Maria sr. Dies, killing herself with Friedrichs weaopn, as he walks away. He hears the shot from outside of their appartment</t>
+  </si>
+  <si>
+    <t>Alois Großbërge von Tolnzar becomes the Werewolf Fury</t>
+  </si>
+  <si>
+    <t>Marina arrives home with her hubsand Wilhelm, there she meets her son and attendance. She later has sex with her 
 husband to cope, bad dreams keeping her awake.</t>
   </si>
   <si>
-    <t>Friedrich has been brought home and Marina rides home with Alexander, questioning Michael about the Wardens</t>
-  </si>
-  <si>
-    <t>Marina, Alexander, Michael, Wilhelm</t>
-  </si>
-  <si>
-    <t>Marina, Wilheml Freiherr, Philipp</t>
-  </si>
-  <si>
-    <t>Marina, Gundel</t>
-  </si>
-  <si>
-    <t>Josef, August, Ingenheim, Ashen-One, Lady of the Cult</t>
-  </si>
-  <si>
-    <t>Continuing Marina wakes up and remmebers the Counts boat, searching in it for clues</t>
-  </si>
-  <si>
-    <t>Friedrich, Marina, Alexander, Anna, Sabine, Helene Berthold, Nai, Sir Charles, etc.</t>
-  </si>
-  <si>
-    <t>Friedrich is talking with his demented mom about life</t>
-  </si>
-  <si>
-    <t>Friedrich, Walburga Pfeiffer</t>
-  </si>
-  <si>
-    <t>Marina, Wilhelm, Philipp, Christoff Bauer, Gundel Götz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meeting of the Wardens and </t>
-  </si>
-  <si>
-    <t>Murder on the Christmasmarket and ensuing chaos</t>
-  </si>
-  <si>
-    <t>Anna catches the killer while Alexander has visions through Maximilian</t>
-  </si>
-  <si>
-    <t>The Trio gets ist name and talks about their plans to make a decision</t>
-  </si>
-  <si>
-    <t>Anna gets trained by Sabine and learns about the Wardens</t>
-  </si>
-  <si>
-    <t>Josef and August learn more about the strange happenings around the Count von Tölz and run into Count von Ingenheim</t>
-  </si>
-  <si>
-    <t>Alexander wakes up from his visions</t>
-  </si>
-  <si>
-    <t>Alexander, Helene</t>
-  </si>
-  <si>
-    <t>January</t>
-  </si>
-  <si>
-    <t>Book1/13</t>
-  </si>
-  <si>
-    <t>Book1/1</t>
-  </si>
-  <si>
-    <t>Book1/2</t>
-  </si>
-  <si>
-    <t>Book1/3</t>
-  </si>
-  <si>
-    <t>Book1/4</t>
-  </si>
-  <si>
-    <t>Book1/5</t>
-  </si>
-  <si>
-    <t>Book1/6</t>
-  </si>
-  <si>
-    <t>Book1/7</t>
-  </si>
-  <si>
-    <t>Book1/8</t>
-  </si>
-  <si>
-    <t>Book1/9</t>
-  </si>
-  <si>
-    <t>Book1/10</t>
-  </si>
-  <si>
-    <t>Book1/17</t>
-  </si>
-  <si>
-    <t>Book1/11</t>
-  </si>
-  <si>
-    <t>Book1/12</t>
-  </si>
-  <si>
-    <t>Book1/18</t>
-  </si>
-  <si>
-    <t>Book1/14</t>
-  </si>
-  <si>
-    <t>Book1/15</t>
-  </si>
-  <si>
-    <t>Book1/16</t>
-  </si>
-  <si>
-    <t>Book1/19</t>
-  </si>
-  <si>
-    <t>Book1/20</t>
-  </si>
-  <si>
-    <t>Book1/21</t>
-  </si>
-  <si>
-    <t>Book1/</t>
-  </si>
-  <si>
-    <t>Alexander trying a 'science' experiment. Older schoolboys bully him for it and his brother Ludwig intervenes, sends Alexander away. He hides and hears his brother die on accident after a push, blacks it from his memories.</t>
-  </si>
-  <si>
-    <t>Alexander goes to Munich to start studying at TUM at 16 years of age</t>
-  </si>
-  <si>
-    <t>Friedrich and Maria talk again about their life together, he notices her frustration forthe first time.</t>
-  </si>
-  <si>
-    <t>Maria sr. Dies, killing herself with Friedrichs weaopn, as he walks away. He hears the shot from outside of their appartment</t>
-  </si>
-  <si>
-    <t>Alois Großbërge von Tolnzar becomes the Werewolf Fury</t>
+    <t>Book 1/18</t>
+  </si>
+  <si>
+    <t>Sabine starts training with Anna to become a Warden</t>
+  </si>
+  <si>
+    <t>Breakfast and ski down the slope. Friedrich hurts himself because of the other Count. A heavy storm begins. Count Großberg leaves them in the Storm and darts off.</t>
   </si>
 </sst>
 </file>
@@ -547,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.88671875" customWidth="1"/>
@@ -581,7 +587,7 @@
         <v>1632</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -725,7 +731,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -743,10 +749,10 @@
         <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F30" t="s">
         <v>19</v>
@@ -759,7 +765,7 @@
     </row>
     <row r="32" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -767,7 +773,7 @@
         <v>2</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -780,7 +786,7 @@
         <v>6</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
@@ -801,7 +807,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -819,13 +825,13 @@
         <v>10</v>
       </c>
       <c r="D41" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F41" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -838,7 +844,7 @@
         <v>28</v>
       </c>
       <c r="D43" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>22</v>
@@ -852,7 +858,7 @@
         <v>29</v>
       </c>
       <c r="D44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>24</v>
@@ -871,7 +877,7 @@
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>27</v>
@@ -885,7 +891,7 @@
         <v>9</v>
       </c>
       <c r="D47" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>29</v>
@@ -896,7 +902,7 @@
     </row>
     <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>31</v>
@@ -907,7 +913,7 @@
     </row>
     <row r="49" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>33</v>
@@ -921,54 +927,54 @@
         <v>10</v>
       </c>
       <c r="D50" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E50" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F50" t="s">
         <v>35</v>
-      </c>
-      <c r="F50" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="51" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E51" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F51" t="s">
         <v>37</v>
-      </c>
-      <c r="F51" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="52" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F52" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -976,35 +982,35 @@
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E55" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F55" t="s">
         <v>42</v>
-      </c>
-      <c r="F55" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="56" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F56" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="F57" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1012,13 +1018,13 @@
         <v>12</v>
       </c>
       <c r="D58" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F58" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1026,10 +1032,10 @@
         <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1037,13 +1043,13 @@
         <v>16</v>
       </c>
       <c r="D60" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F60" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -1051,10 +1057,10 @@
         <v>21</v>
       </c>
       <c r="D61" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F61" t="s">
         <v>23</v>
@@ -1065,79 +1071,87 @@
         <v>22</v>
       </c>
       <c r="D62" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C63">
         <v>23</v>
       </c>
-      <c r="D63" t="s">
-        <v>79</v>
+      <c r="D63" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C64">
+      <c r="D64" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="65" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C65">
         <v>24</v>
       </c>
-      <c r="D64" t="s">
-        <v>86</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F64" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="65" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="F65" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="67" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C67">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="67" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D67" t="s">
+        <v>86</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="68" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C68">
         <v>25</v>
       </c>
-      <c r="D67" t="s">
-        <v>89</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F67" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="68" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C68">
+      <c r="D68" t="s">
+        <v>87</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F68" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="69" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C69">
         <v>27</v>
       </c>
-      <c r="D68" t="s">
-        <v>89</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F68" t="s">
-        <v>66</v>
+      <c r="D69" t="s">
+        <v>87</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F69" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/Buch Bayrische Nächte/Zeitlinie.xlsx
+++ b/Buch Bayrische Nächte/Zeitlinie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julian Dauner\Documents\GitHub\pnpWiki\docs\Buch Bayrische Nächte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEDF0791-F904-4ED4-9EB5-669DAC9107BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6E2768-D94B-49C3-95F9-25142B5D96EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="5205" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -195,9 +195,6 @@
     <t>Friedrich is talking with his demented mom about life</t>
   </si>
   <si>
-    <t>Friedrich, Walburga Pfeiffer</t>
-  </si>
-  <si>
     <t>Marina, Wilhelm, Philipp, Christoff Bauer, Gundel Götz</t>
   </si>
   <si>
@@ -320,6 +317,9 @@
   </si>
   <si>
     <t>Breakfast and ski down the slope. Friedrich hurts himself because of the other Count. A heavy storm begins. Count Großberg leaves them in the Storm and darts off.</t>
+  </si>
+  <si>
+    <t>Friedrich, Waltraut Pfeiffer</t>
   </si>
 </sst>
 </file>
@@ -587,7 +587,7 @@
         <v>1632</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -731,7 +731,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -749,7 +749,7 @@
         <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>46</v>
@@ -765,7 +765,7 @@
     </row>
     <row r="32" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -773,7 +773,7 @@
         <v>2</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -786,7 +786,7 @@
         <v>6</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
@@ -807,7 +807,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -825,7 +825,7 @@
         <v>10</v>
       </c>
       <c r="D41" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>20</v>
@@ -844,7 +844,7 @@
         <v>28</v>
       </c>
       <c r="D43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>22</v>
@@ -858,7 +858,7 @@
         <v>29</v>
       </c>
       <c r="D44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>24</v>
@@ -877,7 +877,7 @@
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>27</v>
@@ -891,7 +891,7 @@
         <v>9</v>
       </c>
       <c r="D47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>29</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>31</v>
@@ -913,7 +913,7 @@
     </row>
     <row r="49" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>33</v>
@@ -927,10 +927,10 @@
         <v>10</v>
       </c>
       <c r="D50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F50" t="s">
         <v>35</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="51" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>36</v>
@@ -949,7 +949,7 @@
     </row>
     <row r="52" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>38</v>
@@ -960,7 +960,7 @@
     </row>
     <row r="53" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>39</v>
@@ -968,7 +968,7 @@
     </row>
     <row r="54" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>45</v>
@@ -982,7 +982,7 @@
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>41</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="56" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>47</v>
@@ -1004,13 +1004,13 @@
     </row>
     <row r="57" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F57" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1018,7 +1018,7 @@
         <v>12</v>
       </c>
       <c r="D58" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>52</v>
@@ -1032,10 +1032,10 @@
         <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1043,13 +1043,13 @@
         <v>16</v>
       </c>
       <c r="D60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F60" t="s">
-        <v>55</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -1057,7 +1057,7 @@
         <v>21</v>
       </c>
       <c r="D61" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>43</v>
@@ -1071,10 +1071,10 @@
         <v>22</v>
       </c>
       <c r="D62" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -1082,18 +1082,18 @@
         <v>23</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="D64" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="65" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -1101,10 +1101,10 @@
         <v>24</v>
       </c>
       <c r="D65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F65" t="s">
         <v>53</v>
@@ -1112,18 +1112,18 @@
     </row>
     <row r="66" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="67" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1131,7 +1131,7 @@
         <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>44</v>
@@ -1145,13 +1145,13 @@
         <v>27</v>
       </c>
       <c r="D69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E69" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F69" t="s">
         <v>63</v>
-      </c>
-      <c r="F69" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/Buch Bayrische Nächte/Zeitlinie.xlsx
+++ b/Buch Bayrische Nächte/Zeitlinie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julian Dauner\Documents\GitHub\pnpWiki\docs\Buch Bayrische Nächte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6E2768-D94B-49C3-95F9-25142B5D96EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2D3369-40BE-46C7-A35D-2C6E2A871411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="5205" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="100">
   <si>
     <t>Year</t>
   </si>
@@ -320,6 +320,15 @@
   </si>
   <si>
     <t>Friedrich, Waltraut Pfeiffer</t>
+  </si>
+  <si>
+    <t>Michael wants to kill himself but falters. Ends up saving Maximilian from Temprests  and vows to keep going.</t>
+  </si>
+  <si>
+    <t>Michael, Maximilian</t>
+  </si>
+  <si>
+    <t>Michaels wife Bärbel dies of stomach cancer and he loses hope, vanishes from sight for half a year. His brewery is continued running by his staff and brewmaster.</t>
   </si>
 </sst>
 </file>
@@ -553,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.88671875" customWidth="1"/>
@@ -812,345 +821,384 @@
     </row>
     <row r="39" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>1882</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C41">
+        <v>8</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
         <v>10</v>
-      </c>
-      <c r="D41" t="s">
-        <v>66</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F41" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B42" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C43">
-        <v>28</v>
-      </c>
-      <c r="D43" t="s">
-        <v>67</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F43" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C44">
-        <v>29</v>
-      </c>
-      <c r="D44" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="F44" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B45" t="s">
-        <v>26</v>
+      <c r="A45">
+        <v>1882</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C46">
-        <v>8</v>
-      </c>
-      <c r="D46" t="s">
-        <v>68</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F46" t="s">
-        <v>28</v>
+      <c r="B46" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C47">
+        <v>10</v>
+      </c>
+      <c r="D47" t="s">
+        <v>66</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C49">
+        <v>28</v>
+      </c>
+      <c r="D49" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F49" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C50">
+        <v>29</v>
+      </c>
+      <c r="D50" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C52">
+        <v>8</v>
+      </c>
+      <c r="D52" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F52" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C53">
         <v>9</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D53" t="s">
         <v>68</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F53" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="D48" t="s">
+    <row r="54" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D54" t="s">
         <v>69</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E54" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F54" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="D49" t="s">
+    <row r="55" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D55" t="s">
         <v>70</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F55" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C50">
+    <row r="56" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C56">
         <v>10</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D56" t="s">
         <v>71</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E56" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F56" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="D51" t="s">
+    <row r="57" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D57" t="s">
         <v>72</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F57" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="D52" t="s">
+    <row r="58" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D58" t="s">
         <v>73</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F58" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="D53" t="s">
+    <row r="59" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D59" t="s">
         <v>74</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="D54" t="s">
+    <row r="60" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D60" t="s">
         <v>75</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E60" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F60" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C55">
+    <row r="61" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C61">
         <v>11</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D61" t="s">
         <v>76</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F61" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D56" t="s">
+    <row r="62" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D62" t="s">
         <v>77</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E62" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F62" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="57" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="D57" t="s">
+    <row r="63" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D63" t="s">
         <v>78</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E63" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F63" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C58">
+    <row r="64" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C64">
         <v>12</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D64" t="s">
         <v>78</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F64" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C59">
+    <row r="65" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C65">
         <v>13</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D65" t="s">
         <v>79</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E65" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C60">
+    <row r="66" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C66">
         <v>16</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D66" t="s">
         <v>80</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E66" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F66" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C61">
+    <row r="67" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C67">
         <v>21</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D67" t="s">
         <v>81</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F67" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C62">
+    <row r="68" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C68">
         <v>22</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D68" t="s">
         <v>82</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E68" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C63">
+    <row r="69" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C69">
         <v>23</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E69" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="D64" s="1" t="s">
+    <row r="70" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D70" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E70" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="65" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C65">
+    <row r="71" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C71">
         <v>24</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D71" t="s">
         <v>83</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F71" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="66" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="D66" t="s">
+    <row r="72" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D72" t="s">
         <v>84</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="D67" t="s">
+    <row r="73" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D73" t="s">
         <v>85</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E73" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C68">
+    <row r="74" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C74">
         <v>25</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D74" t="s">
         <v>86</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F74" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C69">
+    <row r="75" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C75">
         <v>27</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D75" t="s">
         <v>86</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F69" t="s">
+      <c r="F75" t="s">
         <v>63</v>
       </c>
     </row>
